--- a/groundstations.xlsx
+++ b/groundstations.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -447,6 +447,9 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -495,6 +498,21 @@
           <t>Body</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Antenna gain (dBi)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>System noise temp (K)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tx power (W)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -522,6 +540,15 @@
           <t>2-way</t>
         </is>
       </c>
+      <c r="J2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>150</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,9 +581,18 @@
           <t>Moon</t>
         </is>
       </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
+        <v>250</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="12">
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Name" prompt="Shown as the label in the viewer. Must be unique."/>
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Latitude" prompt="Decimal degrees, north positive (28.6083), or 28.6083 N, or 28 36 30.2 N."/>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Longitude" prompt="Decimal degrees, east positive (-80.6043), or 80.6043 W, or 80 36 15.6 W."/>
@@ -570,6 +606,9 @@
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Body" error="Choose Earth or Moon." promptTitle="Body" prompt="Earth or Moon. Blank = Earth. Moon: ground elevation is metres above the mean lunar radius (1737.4 km), blank = 0; it is not looked up." type="list">
       <formula1>"Earth,Moon"</formula1>
     </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Antenna gain" prompt="The station antenna's gain, dBi (e.g. a 3.7 m S-band dish ~37 dBi). Needed for link budgets."/>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="System noise temperature" prompt="Receive system noise temperature, kelvin (e.g. 150 K). With the gain it gives the station's G/T."/>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Transmit power" prompt="Uplink transmit power, watts. Only used for 2-way links."/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -581,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -718,7 +757,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -737,6 +775,30 @@
       <c r="A25" t="inlineStr">
         <is>
           <t>A station's link line and passes also need the line of sight to miss the Earth and the Moon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Antenna gain (dBi), System noise temp (K), Tx power (W) - columns J-L, optional: the station's radio for</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    link budgets. Gain and noise temperature give its G/T (downlink); Tx power its uplink (2-way only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    The spacecraft side is in spacecraft.xlsx, sheet Payloads. The example values are illustrative.</t>
         </is>
       </c>
     </row>

--- a/groundstations.xlsx
+++ b/groundstations.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Ground stations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="How to" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Station radios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="How to" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -529,9 +530,6 @@
       <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" t="n">
-        <v>2250</v>
-      </c>
       <c r="G2" t="n">
         <v>170</v>
       </c>
@@ -540,15 +538,6 @@
           <t>2-way</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K2" t="n">
-        <v>150</v>
-      </c>
-      <c r="L2" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,9 +554,6 @@
       <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
-        <v>2250</v>
-      </c>
       <c r="G3" t="n">
         <v>160</v>
       </c>
@@ -581,14 +567,63 @@
           <t>Moon</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>250</v>
-      </c>
-      <c r="L3" t="n">
-        <v>20</v>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lunar south pole</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-89.59999999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>145.22351</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>170</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2-way</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Moon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LID 1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-89.4545</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-145.2232</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>170</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2-way</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Moon</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -620,7 +655,229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Downlink (MHz)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Uplink (MHz)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Antenna gain (dBi)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>System noise temp (K)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tx power (W)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Example station</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S-band</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Example station</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>X-band</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7190</v>
+      </c>
+      <c r="E3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Example lunar station</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S-band</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lunar south pole</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X-band</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7190</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LID 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S-band</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LID 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>X-band</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7190</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>150</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -646,7 +903,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Row 2 is an example: replace or delete it.</t>
+          <t>The rows are examples: replace or delete them. Radios are on the Station radios sheet.</t>
         </is>
       </c>
     </row>
@@ -698,7 +955,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Frequency (MHz) - operating frequency, e.g. 2250 for S-band, 8400 for X-band.</t>
+          <t>Frequency (MHz) - optional, old single-radio form: used only if the station has no rows on the Station radios sheet.</t>
         </is>
       </c>
     </row>
@@ -757,6 +1014,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -778,27 +1036,53 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Antenna gain (dBi), System noise temp (K), Tx power (W) - columns J-L, optional: the station's radio for</t>
+          <t>Antenna gain, System noise temp, Tx power - columns J-L: the old single-radio form, as Frequency.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    link budgets. Gain and noise temperature give its G/T (downlink); Tx power its uplink (2-way only).</t>
+          <t>Station radios sheet - one row per antenna / band a station supports, any number per station:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    The spacecraft side is in spacecraft.xlsx, sheet Payloads. The example values are illustrative.</t>
+          <t xml:space="preserve">    Station (its name on the Ground stations sheet) | Radio (a name; blank = its band)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Downlink (MHz) - what it receives; sets the band (S 2-4 GHz, X 8-12, Ka 27-40 ...). It works with every</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    spacecraft radio in the same band (spacecraft.xlsx, sheet Radios).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Uplink (MHz) - what it transmits on a 2-way link (blank = the spacecraft radio's uplink frequency).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Antenna gain + System noise temp give its G/T (downlink); Tx power + gain its uplink. Values are illustrative.</t>
         </is>
       </c>
     </row>
